--- a/data/trans_orig/P2B_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2B_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2007</t>
+          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37898</t>
+          <t>37950</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62343</t>
+          <t>62368</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36044</t>
+          <t>36009</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61207</t>
+          <t>60058</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80750</t>
+          <t>79365</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116019</t>
+          <t>114761</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>189033</t>
+          <t>189008</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>213478</t>
+          <t>213426</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>234335</t>
+          <t>235484</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259498</t>
+          <t>259533</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>430898</t>
+          <t>432156</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>466167</t>
+          <t>467552</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,49%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109211</t>
+          <t>106971</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>146187</t>
+          <t>147071</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>148163</t>
+          <t>147215</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>191331</t>
+          <t>191877</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>269680</t>
+          <t>268648</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>325349</t>
+          <t>325117</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,25%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>283240</t>
+          <t>282356</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>320216</t>
+          <t>322456</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>301467</t>
+          <t>300921</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>344635</t>
+          <t>345583</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>596876</t>
+          <t>597108</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>652545</t>
+          <t>653577</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,87%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>130111</t>
+          <t>127979</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>172454</t>
+          <t>171616</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>171493</t>
+          <t>171281</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>217718</t>
+          <t>218741</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>314085</t>
+          <t>312870</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>375541</t>
+          <t>376005</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,38%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>380477</t>
+          <t>381315</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>422820</t>
+          <t>424952</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>427771</t>
+          <t>426748</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>473996</t>
+          <t>474208</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>822878</t>
+          <t>822414</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>884334</t>
+          <t>885549</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,89%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52528</t>
+          <t>51859</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81370</t>
+          <t>82062</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65655</t>
+          <t>65371</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97893</t>
+          <t>96435</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126269</t>
+          <t>125951</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>170145</t>
+          <t>171565</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>328114</t>
+          <t>327422</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>356956</t>
+          <t>357625</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>318361</t>
+          <t>319819</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>350599</t>
+          <t>350883</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>655593</t>
+          <t>654173</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>699469</t>
+          <t>699787</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,75%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36292</t>
+          <t>36314</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61154</t>
+          <t>61528</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56734</t>
+          <t>57261</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88397</t>
+          <t>87027</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>97956</t>
+          <t>99435</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136638</t>
+          <t>138241</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>258579</t>
+          <t>258205</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>283441</t>
+          <t>283419</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>258133</t>
+          <t>259503</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>289796</t>
+          <t>289269</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>529624</t>
+          <t>528021</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>568306</t>
+          <t>566827</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,08%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31455</t>
+          <t>31022</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54871</t>
+          <t>54769</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66810</t>
+          <t>67982</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96470</t>
+          <t>98681</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>103447</t>
+          <t>102332</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>142152</t>
+          <t>141656</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236778</t>
+          <t>236880</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260194</t>
+          <t>260627</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>246464</t>
+          <t>244253</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>276124</t>
+          <t>274952</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>492431</t>
+          <t>492927</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>531136</t>
+          <t>532251</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,87%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46944</t>
+          <t>46220</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72909</t>
+          <t>71459</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>90933</t>
+          <t>91621</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>126125</t>
+          <t>125762</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>146543</t>
+          <t>144804</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>191477</t>
+          <t>190930</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,11%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>136974</t>
+          <t>138424</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>162939</t>
+          <t>163663</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>207783</t>
+          <t>208146</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>242975</t>
+          <t>242287</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>352314</t>
+          <t>352861</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>397248</t>
+          <t>398987</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,37%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>498707</t>
+          <t>498664</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>579750</t>
+          <t>585848</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>710346</t>
+          <t>705160</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>800129</t>
+          <t>801015</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1229084</t>
+          <t>1231143</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1358587</t>
+          <t>1358193</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1884733</t>
+          <t>1878635</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1965776</t>
+          <t>1965819</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2073324</t>
+          <t>2072438</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2163107</t>
+          <t>2168293</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3979349</t>
+          <t>3979743</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4108852</t>
+          <t>4106793</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,94%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2012</t>
+          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>115759</t>
+          <t>115893</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>147133</t>
+          <t>148161</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>140822</t>
+          <t>138697</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>174408</t>
+          <t>174063</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>266563</t>
+          <t>264132</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>314170</t>
+          <t>311179</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,15%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>113979</t>
+          <t>112951</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>145353</t>
+          <t>145219</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>128695</t>
+          <t>129040</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>162281</t>
+          <t>164406</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>250045</t>
+          <t>253036</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>297652</t>
+          <t>300083</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>53,19%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>235872</t>
+          <t>230587</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>276230</t>
+          <t>276791</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>361361</t>
+          <t>360964</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>399486</t>
+          <t>398722</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>606135</t>
+          <t>607277</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>665202</t>
+          <t>666835</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,4%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>184038</t>
+          <t>183477</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>224396</t>
+          <t>229681</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>101105</t>
+          <t>101869</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>139230</t>
+          <t>139627</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>295656</t>
+          <t>294023</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>354723</t>
+          <t>353581</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,8%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>423857</t>
+          <t>424710</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>471919</t>
+          <t>470248</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>487357</t>
+          <t>488013</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>530071</t>
+          <t>530310</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>924846</t>
+          <t>927148</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>989452</t>
+          <t>989604</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,29%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143880</t>
+          <t>145551</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>191942</t>
+          <t>191089</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>134485</t>
+          <t>134246</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>177199</t>
+          <t>176543</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>290903</t>
+          <t>290751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>355509</t>
+          <t>353207</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,59%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>248602</t>
+          <t>250074</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>294504</t>
+          <t>296258</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>212685</t>
+          <t>214356</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>260371</t>
+          <t>259413</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>473024</t>
+          <t>472295</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>544217</t>
+          <t>542690</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>52,95%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>200123</t>
+          <t>198369</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>246025</t>
+          <t>244553</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>269865</t>
+          <t>270823</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>317551</t>
+          <t>315880</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>480645</t>
+          <t>482172</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>551838</t>
+          <t>552567</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>53,92%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92101</t>
+          <t>90928</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127865</t>
+          <t>127435</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>111974</t>
+          <t>112133</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>152714</t>
+          <t>151196</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>214895</t>
+          <t>215680</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>266482</t>
+          <t>266149</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,62%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>232647</t>
+          <t>233077</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>268411</t>
+          <t>269584</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>255616</t>
+          <t>257134</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>296356</t>
+          <t>296197</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>502360</t>
+          <t>502693</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>553947</t>
+          <t>553162</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,95%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73954</t>
+          <t>74916</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>107500</t>
+          <t>108761</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>75312</t>
+          <t>75729</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>110196</t>
+          <t>109010</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>160964</t>
+          <t>158351</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>206490</t>
+          <t>208040</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>199518</t>
+          <t>198257</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>233064</t>
+          <t>232102</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>241888</t>
+          <t>243074</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>276772</t>
+          <t>276355</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>452612</t>
+          <t>451062</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>498138</t>
+          <t>500751</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,97%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>99015</t>
+          <t>98013</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>132272</t>
+          <t>131576</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>173282</t>
+          <t>172589</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>214271</t>
+          <t>213646</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>281864</t>
+          <t>282001</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>337598</t>
+          <t>336678</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,14%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>116613</t>
+          <t>117309</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>149870</t>
+          <t>150872</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>170411</t>
+          <t>171036</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>211400</t>
+          <t>212093</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>295970</t>
+          <t>296890</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>351704</t>
+          <t>351567</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,49%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1368979</t>
+          <t>1366860</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1478154</t>
+          <t>1474978</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1645976</t>
+          <t>1642075</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1756874</t>
+          <t>1759869</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3045590</t>
+          <t>3046118</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3212455</t>
+          <t>3207681</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,44%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1270068</t>
+          <t>1273244</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1379243</t>
+          <t>1381362</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1386707</t>
+          <t>1383712</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1497605</t>
+          <t>1501506</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2679348</t>
+          <t>2684122</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2846213</t>
+          <t>2845685</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2016</t>
+          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68950</t>
+          <t>68945</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97940</t>
+          <t>96845</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>98324</t>
+          <t>98971</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>128750</t>
+          <t>127355</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>175852</t>
+          <t>173293</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>217450</t>
+          <t>216360</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,16%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>127458</t>
+          <t>128553</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>156448</t>
+          <t>156453</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>114535</t>
+          <t>115930</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>144961</t>
+          <t>144314</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>251233</t>
+          <t>252323</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>292831</t>
+          <t>295390</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>63,03%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>170501</t>
+          <t>170935</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>206902</t>
+          <t>207778</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>266021</t>
+          <t>267656</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>303986</t>
+          <t>304681</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>447043</t>
+          <t>449509</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>502535</t>
+          <t>502794</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,89%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>131110</t>
+          <t>130234</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>167511</t>
+          <t>167077</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>132832</t>
+          <t>132137</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>170797</t>
+          <t>169162</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>272294</t>
+          <t>272035</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>327786</t>
+          <t>325320</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,99%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>297068</t>
+          <t>297289</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>342916</t>
+          <t>342056</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>358894</t>
+          <t>360159</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>404086</t>
+          <t>405517</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>671516</t>
+          <t>671276</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>735131</t>
+          <t>737205</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,28%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>181222</t>
+          <t>182082</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>227070</t>
+          <t>226849</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>184116</t>
+          <t>182685</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>229308</t>
+          <t>228043</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>377209</t>
+          <t>375135</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>440824</t>
+          <t>441064</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,65%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>178486</t>
+          <t>175592</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>223138</t>
+          <t>221438</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>181330</t>
+          <t>180969</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>225381</t>
+          <t>225616</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>364639</t>
+          <t>366222</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>429162</t>
+          <t>429962</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>263116</t>
+          <t>264816</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>307768</t>
+          <t>310662</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>272185</t>
+          <t>271950</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>316236</t>
+          <t>316597</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>554658</t>
+          <t>553858</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>619181</t>
+          <t>617598</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>62,78%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66262</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97456</t>
+          <t>98545</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>93369</t>
+          <t>92856</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>131139</t>
+          <t>132520</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>170474</t>
+          <t>168433</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>221601</t>
+          <t>220016</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,77%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>244372</t>
+          <t>243283</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>275566</t>
+          <t>276782</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>291828</t>
+          <t>290447</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>329598</t>
+          <t>330111</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>543194</t>
+          <t>544779</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>594321</t>
+          <t>596362</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,98%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58529</t>
+          <t>59915</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>89515</t>
+          <t>90011</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>82957</t>
+          <t>82867</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>117663</t>
+          <t>119372</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>150349</t>
+          <t>150021</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>197895</t>
+          <t>195608</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>238527</t>
+          <t>238031</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269513</t>
+          <t>268127</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>250087</t>
+          <t>248378</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>284793</t>
+          <t>284883</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>497897</t>
+          <t>500184</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>545443</t>
+          <t>545771</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>80261</t>
+          <t>80193</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>107232</t>
+          <t>106771</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>168256</t>
+          <t>170461</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>213540</t>
+          <t>215166</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>259354</t>
+          <t>257716</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>311990</t>
+          <t>312145</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,89%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>148089</t>
+          <t>148550</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>175060</t>
+          <t>175128</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>182995</t>
+          <t>181369</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>228279</t>
+          <t>226074</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>339867</t>
+          <t>339712</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>392503</t>
+          <t>394141</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,46%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>987571</t>
+          <t>992738</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1086042</t>
+          <t>1089928</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1331846</t>
+          <t>1332406</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1444516</t>
+          <t>1446870</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2350037</t>
+          <t>2355148</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2502291</t>
+          <t>2502314</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1412951</t>
+          <t>1409065</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1511422</t>
+          <t>1506255</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1508607</t>
+          <t>1506253</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1621277</t>
+          <t>1620717</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2949825</t>
+          <t>2949802</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3102079</t>
+          <t>3096968</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,8%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2023</t>
+          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13159</t>
+          <t>13486</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43037</t>
+          <t>43727</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21866</t>
+          <t>21987</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48225</t>
+          <t>47787</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42697</t>
+          <t>42777</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81357</t>
+          <t>82313</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>134970</t>
+          <t>134280</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>164848</t>
+          <t>164521</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>97676</t>
+          <t>98114</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>124035</t>
+          <t>123914</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,17 +9848,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>264796</t>
+          <t>264797</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>242550</t>
+          <t>241595</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>281210</t>
+          <t>281131</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,79%</t>
         </is>
       </c>
     </row>
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>323907</t>
+          <t>323908</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>323907</t>
+          <t>323908</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>323907</t>
+          <t>323908</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39838</t>
+          <t>38832</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70748</t>
+          <t>71786</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51912</t>
+          <t>48748</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>129454</t>
+          <t>127363</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99212</t>
+          <t>99225</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>183837</t>
+          <t>185643</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>122682</t>
+          <t>121644</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>153592</t>
+          <t>154598</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>236690</t>
+          <t>238781</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>314232</t>
+          <t>317396</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>375737</t>
+          <t>373931</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>460362</t>
+          <t>460349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>103851</t>
+          <t>103459</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>140870</t>
+          <t>142773</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>100854</t>
+          <t>96643</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>159278</t>
+          <t>159973</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>213845</t>
+          <t>219555</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>290440</t>
+          <t>293203</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>241875</t>
+          <t>239972</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>278894</t>
+          <t>279286</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>358749</t>
+          <t>358054</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>417173</t>
+          <t>421384</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>610333</t>
+          <t>607570</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>686928</t>
+          <t>681218</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>75,63%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88326</t>
+          <t>86977</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122280</t>
+          <t>121814</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88292</t>
+          <t>90262</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>129000</t>
+          <t>128943</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>190462</t>
+          <t>187720</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>242278</t>
+          <t>240934</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>316626</t>
+          <t>317092</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>350580</t>
+          <t>351929</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>386739</t>
+          <t>386796</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>427447</t>
+          <t>425477</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>712367</t>
+          <t>713711</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>764183</t>
+          <t>766925</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>80,34%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51654</t>
+          <t>50637</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78150</t>
+          <t>78819</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59223</t>
+          <t>59270</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>81427</t>
+          <t>80501</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>114615</t>
+          <t>116106</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>150690</t>
+          <t>152275</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>252520</t>
+          <t>251851</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>279016</t>
+          <t>280033</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>274449</t>
+          <t>275375</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>296653</t>
+          <t>296606</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>535856</t>
+          <t>534271</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>571931</t>
+          <t>570440</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,09%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33068</t>
+          <t>34236</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52690</t>
+          <t>53610</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>94606</t>
+          <t>92751</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>465093</t>
+          <t>476815</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>131842</t>
+          <t>131489</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>617467</t>
+          <t>630253</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>64,84%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>311647</t>
+          <t>310727</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>331269</t>
+          <t>330101</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>142510</t>
+          <t>130788</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>512997</t>
+          <t>514852</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>354473</t>
+          <t>341687</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>840098</t>
+          <t>840451</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,47%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>71976</t>
+          <t>72658</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96428</t>
+          <t>96028</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>171268</t>
+          <t>170317</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>200458</t>
+          <t>200210</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>251221</t>
+          <t>249723</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>289227</t>
+          <t>286048</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,53%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>184863</t>
+          <t>185263</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>209315</t>
+          <t>208633</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>223964</t>
+          <t>224212</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>253154</t>
+          <t>254105</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>416486</t>
+          <t>419665</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>454492</t>
+          <t>455990</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,61%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>458338</t>
+          <t>456947</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>541364</t>
+          <t>536612</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>733652</t>
+          <t>735655</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1372674</t>
+          <t>1404661</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1224278</t>
+          <t>1219515</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1953711</t>
+          <t>1961677</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1628023</t>
+          <t>1632775</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1711049</t>
+          <t>1712440</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1561038</t>
+          <t>1529051</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2200060</t>
+          <t>2198057</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3149388</t>
+          <t>3141422</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3878821</t>
+          <t>3883584</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,1%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2B_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2B_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37950</t>
+          <t>37559</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62368</t>
+          <t>61763</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36009</t>
+          <t>35742</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60058</t>
+          <t>60145</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79365</t>
+          <t>77092</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114761</t>
+          <t>113834</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>189008</t>
+          <t>189613</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>213426</t>
+          <t>213817</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>235484</t>
+          <t>235397</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259533</t>
+          <t>259800</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>432156</t>
+          <t>433083</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>467552</t>
+          <t>469825</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,9%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>106971</t>
+          <t>107764</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>147071</t>
+          <t>146940</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>147215</t>
+          <t>148441</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>191877</t>
+          <t>192555</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>268648</t>
+          <t>268834</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>325117</t>
+          <t>326611</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,42%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>282356</t>
+          <t>282487</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>322456</t>
+          <t>321663</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>300921</t>
+          <t>300243</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>345583</t>
+          <t>344357</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>597108</t>
+          <t>595614</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>653577</t>
+          <t>653391</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,85%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>127979</t>
+          <t>128437</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>171616</t>
+          <t>171821</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>171281</t>
+          <t>170795</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>218741</t>
+          <t>216373</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>312870</t>
+          <t>309184</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>376005</t>
+          <t>374361</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,24%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>381315</t>
+          <t>381110</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>424952</t>
+          <t>424494</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>426748</t>
+          <t>429116</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>474208</t>
+          <t>474694</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>822414</t>
+          <t>824058</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>885549</t>
+          <t>889235</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,2%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51859</t>
+          <t>51626</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82062</t>
+          <t>81480</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65371</t>
+          <t>64113</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96435</t>
+          <t>97389</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125951</t>
+          <t>126339</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>171565</t>
+          <t>171995</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>327422</t>
+          <t>328004</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>357625</t>
+          <t>357858</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>319819</t>
+          <t>318865</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>350883</t>
+          <t>352141</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>654173</t>
+          <t>653743</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>699787</t>
+          <t>699399</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,7%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36314</t>
+          <t>35084</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61528</t>
+          <t>61555</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57261</t>
+          <t>56821</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87027</t>
+          <t>87742</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99435</t>
+          <t>100128</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>138241</t>
+          <t>138286</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>258205</t>
+          <t>258178</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>283419</t>
+          <t>284649</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>259503</t>
+          <t>258788</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>289269</t>
+          <t>289709</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>528021</t>
+          <t>527976</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>566827</t>
+          <t>566134</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,97%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31022</t>
+          <t>31151</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54769</t>
+          <t>54396</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67982</t>
+          <t>66935</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>98681</t>
+          <t>97019</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102332</t>
+          <t>105206</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>141656</t>
+          <t>143328</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236880</t>
+          <t>237253</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260627</t>
+          <t>260498</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>244253</t>
+          <t>245915</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>274952</t>
+          <t>275999</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>492927</t>
+          <t>491255</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>532251</t>
+          <t>529377</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,42%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46220</t>
+          <t>47631</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71459</t>
+          <t>73124</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>91621</t>
+          <t>91665</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>125762</t>
+          <t>126014</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>144804</t>
+          <t>144159</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>190930</t>
+          <t>190293</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,99%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>138424</t>
+          <t>136759</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>163663</t>
+          <t>162252</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>208146</t>
+          <t>207894</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>242287</t>
+          <t>242243</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>352861</t>
+          <t>353498</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>398987</t>
+          <t>399632</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,49%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>498664</t>
+          <t>494437</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>585848</t>
+          <t>581117</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>705160</t>
+          <t>705373</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>801015</t>
+          <t>797847</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1231143</t>
+          <t>1230628</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1358193</t>
+          <t>1358434</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1878635</t>
+          <t>1883366</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1965819</t>
+          <t>1970046</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2072438</t>
+          <t>2075606</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2168293</t>
+          <t>2168080</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3979743</t>
+          <t>3979502</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4106793</t>
+          <t>4107308</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,95%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>115893</t>
+          <t>114173</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>148161</t>
+          <t>147388</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>138697</t>
+          <t>139814</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>174063</t>
+          <t>173478</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>264132</t>
+          <t>265267</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>311179</t>
+          <t>311327</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,18%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>112951</t>
+          <t>113724</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>145219</t>
+          <t>146939</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129040</t>
+          <t>129625</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>164406</t>
+          <t>163289</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>253036</t>
+          <t>252888</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>300083</t>
+          <t>298948</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>52,98%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>230587</t>
+          <t>235351</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>276791</t>
+          <t>276636</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>360964</t>
+          <t>361102</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>398722</t>
+          <t>399165</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>607277</t>
+          <t>608027</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>666835</t>
+          <t>667230</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,44%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>183477</t>
+          <t>183632</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>229681</t>
+          <t>224917</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>101869</t>
+          <t>101426</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>139627</t>
+          <t>139489</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>294023</t>
+          <t>293628</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>353581</t>
+          <t>352831</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,72%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>424710</t>
+          <t>425038</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>470248</t>
+          <t>469966</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>488013</t>
+          <t>487554</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>530310</t>
+          <t>532138</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>927148</t>
+          <t>926894</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>989604</t>
+          <t>991390</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,43%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>145551</t>
+          <t>145833</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>191089</t>
+          <t>190761</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>134246</t>
+          <t>132418</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>176543</t>
+          <t>177002</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>290751</t>
+          <t>288965</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>353207</t>
+          <t>353461</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,61%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>250074</t>
+          <t>248023</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>296258</t>
+          <t>293643</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>214356</t>
+          <t>211943</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>259413</t>
+          <t>264038</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>472295</t>
+          <t>473119</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>542690</t>
+          <t>543572</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>53,04%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>198369</t>
+          <t>200984</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>244553</t>
+          <t>246604</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>270823</t>
+          <t>266198</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>315880</t>
+          <t>318293</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>482172</t>
+          <t>481290</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>552567</t>
+          <t>551743</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,84%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>90928</t>
+          <t>89290</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127435</t>
+          <t>126499</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>112133</t>
+          <t>112019</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>151196</t>
+          <t>151603</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>215680</t>
+          <t>212959</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>266149</t>
+          <t>265409</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>233077</t>
+          <t>234013</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>269584</t>
+          <t>271222</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>257134</t>
+          <t>256727</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>296197</t>
+          <t>296311</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>502693</t>
+          <t>503433</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>553162</t>
+          <t>555883</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>72,3%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74916</t>
+          <t>73817</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>108761</t>
+          <t>108474</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>75729</t>
+          <t>76367</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>109010</t>
+          <t>109334</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>158351</t>
+          <t>160775</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>208040</t>
+          <t>208976</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>198257</t>
+          <t>198544</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>232102</t>
+          <t>233201</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>243074</t>
+          <t>242750</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>276355</t>
+          <t>275717</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>451062</t>
+          <t>450126</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>500751</t>
+          <t>498327</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>75,61%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>98013</t>
+          <t>98474</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>131576</t>
+          <t>133800</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>172589</t>
+          <t>172904</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>213646</t>
+          <t>212964</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>282001</t>
+          <t>280349</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>336678</t>
+          <t>334104</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>52,73%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>117309</t>
+          <t>115085</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>150872</t>
+          <t>150411</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>171036</t>
+          <t>171718</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>212093</t>
+          <t>211778</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>296890</t>
+          <t>299464</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>351567</t>
+          <t>353219</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,75%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1366860</t>
+          <t>1366682</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1474978</t>
+          <t>1477050</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1642075</t>
+          <t>1646138</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1759869</t>
+          <t>1755358</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3046118</t>
+          <t>3038954</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3207681</t>
+          <t>3202251</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,35%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1273244</t>
+          <t>1271172</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1381362</t>
+          <t>1381540</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1383712</t>
+          <t>1388223</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1501506</t>
+          <t>1497443</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2684122</t>
+          <t>2689552</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2845685</t>
+          <t>2852849</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,42%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68945</t>
+          <t>68597</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96845</t>
+          <t>98978</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>98971</t>
+          <t>98925</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127355</t>
+          <t>128713</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>173293</t>
+          <t>176256</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>216360</t>
+          <t>218094</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,53%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>128553</t>
+          <t>126420</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>156453</t>
+          <t>156801</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>115930</t>
+          <t>114572</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>144314</t>
+          <t>144360</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>252323</t>
+          <t>250589</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>295390</t>
+          <t>292427</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,39%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>170935</t>
+          <t>170954</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>207778</t>
+          <t>207964</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>267656</t>
+          <t>264301</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>304681</t>
+          <t>304290</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>449509</t>
+          <t>449294</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>502794</t>
+          <t>500713</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,62%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>130234</t>
+          <t>130048</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>167077</t>
+          <t>167058</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>132137</t>
+          <t>132528</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>169162</t>
+          <t>172517</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>272035</t>
+          <t>274116</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>325320</t>
+          <t>325535</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,01%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>297289</t>
+          <t>295476</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>342056</t>
+          <t>341229</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>360159</t>
+          <t>360038</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>405517</t>
+          <t>404626</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>671276</t>
+          <t>671428</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>737205</t>
+          <t>733110</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>65,91%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>182082</t>
+          <t>182909</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>226849</t>
+          <t>228662</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>182685</t>
+          <t>183576</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>228043</t>
+          <t>228164</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>375135</t>
+          <t>379230</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>441064</t>
+          <t>440912</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>175592</t>
+          <t>177784</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>221438</t>
+          <t>221495</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>180969</t>
+          <t>178418</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>225616</t>
+          <t>223794</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>366222</t>
+          <t>368946</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>429962</t>
+          <t>431058</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,81%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>264816</t>
+          <t>264759</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>310662</t>
+          <t>308470</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>271950</t>
+          <t>273772</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>316597</t>
+          <t>319148</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>553858</t>
+          <t>552762</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>617598</t>
+          <t>614874</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,5%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65046</t>
+          <t>65568</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98545</t>
+          <t>96904</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92856</t>
+          <t>92822</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>132520</t>
+          <t>131914</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>168433</t>
+          <t>170631</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>220016</t>
+          <t>219534</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,7%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>243283</t>
+          <t>244924</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>276782</t>
+          <t>276260</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>290447</t>
+          <t>291053</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>330111</t>
+          <t>330145</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>544779</t>
+          <t>545261</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>596362</t>
+          <t>594164</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,69%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59915</t>
+          <t>58134</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>90011</t>
+          <t>88730</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>82867</t>
+          <t>84456</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>119372</t>
+          <t>118111</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>150021</t>
+          <t>152427</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>195608</t>
+          <t>199307</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>238031</t>
+          <t>239312</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268127</t>
+          <t>269908</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>248378</t>
+          <t>249639</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>284883</t>
+          <t>283294</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>500184</t>
+          <t>496485</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>545771</t>
+          <t>543365</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,09%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>80193</t>
+          <t>79515</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>106771</t>
+          <t>107194</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>170461</t>
+          <t>168644</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>215166</t>
+          <t>213854</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>257716</t>
+          <t>257633</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>312145</t>
+          <t>311832</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,84%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>148550</t>
+          <t>148127</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>175128</t>
+          <t>175806</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>181369</t>
+          <t>182681</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>226074</t>
+          <t>227891</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>339712</t>
+          <t>340025</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>394141</t>
+          <t>394224</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,48%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>992738</t>
+          <t>989298</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1089928</t>
+          <t>1093685</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1332406</t>
+          <t>1329864</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1446870</t>
+          <t>1438320</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2355148</t>
+          <t>2346271</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2502314</t>
+          <t>2495542</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1409065</t>
+          <t>1405308</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1506255</t>
+          <t>1509695</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1506253</t>
+          <t>1514803</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1620717</t>
+          <t>1623259</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2949802</t>
+          <t>2956574</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3096968</t>
+          <t>3105845</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,97%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>31803</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13486</t>
+          <t>18490</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43727</t>
+          <t>51389</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>33487</t>
+          <t>45374</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21987</t>
+          <t>31429</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47787</t>
+          <t>63017</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>59111</t>
+          <t>77177</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42777</t>
+          <t>55819</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82313</t>
+          <t>100615</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>152384</t>
+          <t>139493</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>134280</t>
+          <t>119907</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>164521</t>
+          <t>152806</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>112414</t>
+          <t>131279</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>98114</t>
+          <t>113636</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>123914</t>
+          <t>145224</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>264797</t>
+          <t>270772</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>241595</t>
+          <t>247334</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>281131</t>
+          <t>292130</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>83,96%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>178007</t>
+          <t>171296</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>178007</t>
+          <t>171296</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>178007</t>
+          <t>171296</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>145901</t>
+          <t>176653</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>145901</t>
+          <t>176653</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>145901</t>
+          <t>176653</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>323908</t>
+          <t>347949</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>323908</t>
+          <t>347949</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>323908</t>
+          <t>347949</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53653</t>
+          <t>69504</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38832</t>
+          <t>52542</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71786</t>
+          <t>87848</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>97734</t>
+          <t>113896</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48748</t>
+          <t>96587</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>127363</t>
+          <t>133617</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>151388</t>
+          <t>183400</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99225</t>
+          <t>157755</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>185643</t>
+          <t>211196</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>37,78%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>139777</t>
+          <t>151567</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>121644</t>
+          <t>133223</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154598</t>
+          <t>168529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>268410</t>
+          <t>224111</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>238781</t>
+          <t>204390</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>317396</t>
+          <t>241420</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>408186</t>
+          <t>375678</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>373931</t>
+          <t>347882</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>460349</t>
+          <t>401323</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>71,78%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>193430</t>
+          <t>221071</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>193430</t>
+          <t>221071</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>193430</t>
+          <t>221071</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>366144</t>
+          <t>338007</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>366144</t>
+          <t>338007</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>366144</t>
+          <t>338007</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>559574</t>
+          <t>559078</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>559574</t>
+          <t>559078</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>559574</t>
+          <t>559078</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>121202</t>
+          <t>143860</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>103459</t>
+          <t>122350</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142773</t>
+          <t>164514</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>138106</t>
+          <t>159873</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96643</t>
+          <t>143448</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>159973</t>
+          <t>180463</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>259308</t>
+          <t>303732</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>219555</t>
+          <t>277843</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>293203</t>
+          <t>333826</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>34,21%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>261543</t>
+          <t>293111</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>239972</t>
+          <t>272457</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>279286</t>
+          <t>314621</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>379921</t>
+          <t>379092</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>358054</t>
+          <t>358502</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>421384</t>
+          <t>395517</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>641465</t>
+          <t>672204</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>607570</t>
+          <t>642110</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>681218</t>
+          <t>698093</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>71,53%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>382745</t>
+          <t>436971</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>382745</t>
+          <t>436971</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>382745</t>
+          <t>436971</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>518027</t>
+          <t>538965</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>518027</t>
+          <t>538965</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>518027</t>
+          <t>538965</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>900773</t>
+          <t>975936</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>900773</t>
+          <t>975936</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>900773</t>
+          <t>975936</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>105524</t>
+          <t>120486</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86977</t>
+          <t>100096</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121814</t>
+          <t>141552</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>111273</t>
+          <t>127434</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90262</t>
+          <t>113216</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128943</t>
+          <t>144205</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>216797</t>
+          <t>247920</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>187720</t>
+          <t>223413</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>240934</t>
+          <t>273953</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>333382</t>
+          <t>360983</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>317092</t>
+          <t>339917</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>351929</t>
+          <t>381373</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>404466</t>
+          <t>399914</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>386796</t>
+          <t>383143</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>425477</t>
+          <t>414132</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>737848</t>
+          <t>760897</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>713711</t>
+          <t>734864</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>766925</t>
+          <t>785404</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>77,85%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>438906</t>
+          <t>481469</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>438906</t>
+          <t>481469</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>438906</t>
+          <t>481469</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>515739</t>
+          <t>527348</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>515739</t>
+          <t>527348</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>515739</t>
+          <t>527348</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>954645</t>
+          <t>1008817</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>954645</t>
+          <t>1008817</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>954645</t>
+          <t>1008817</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>63815</t>
+          <t>68899</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50637</t>
+          <t>55989</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78819</t>
+          <t>85612</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>69434</t>
+          <t>78031</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59270</t>
+          <t>65216</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80501</t>
+          <t>91344</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>133249</t>
+          <t>146930</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>116106</t>
+          <t>130800</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>152275</t>
+          <t>167703</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>266855</t>
+          <t>284509</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>251851</t>
+          <t>267796</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>280033</t>
+          <t>297419</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>286442</t>
+          <t>320925</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>275375</t>
+          <t>307612</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>296606</t>
+          <t>333740</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>553297</t>
+          <t>605434</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>534271</t>
+          <t>584661</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>570440</t>
+          <t>621564</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,61%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>330670</t>
+          <t>353408</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>330670</t>
+          <t>353408</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>330670</t>
+          <t>353408</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>355876</t>
+          <t>398956</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>355876</t>
+          <t>398956</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>355876</t>
+          <t>398956</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>686546</t>
+          <t>752364</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>686546</t>
+          <t>752364</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>686546</t>
+          <t>752364</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>42396</t>
+          <t>46262</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34236</t>
+          <t>36354</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53610</t>
+          <t>57537</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>269918</t>
+          <t>73173</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>92751</t>
+          <t>62390</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>476815</t>
+          <t>85879</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>312314</t>
+          <t>119436</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>131489</t>
+          <t>104770</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>630253</t>
+          <t>135186</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>321941</t>
+          <t>356448</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>310727</t>
+          <t>345173</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>330101</t>
+          <t>366356</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>337685</t>
+          <t>365182</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>130788</t>
+          <t>352476</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>514852</t>
+          <t>375965</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>659626</t>
+          <t>721629</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>341687</t>
+          <t>705879</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>840451</t>
+          <t>736295</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>87,54%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>364337</t>
+          <t>402710</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>364337</t>
+          <t>402710</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>364337</t>
+          <t>402710</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607603</t>
+          <t>438355</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607603</t>
+          <t>438355</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607603</t>
+          <t>438355</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>971940</t>
+          <t>841065</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>971940</t>
+          <t>841065</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>971940</t>
+          <t>841065</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>83956</t>
+          <t>90436</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72658</t>
+          <t>77045</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96028</t>
+          <t>105181</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>185009</t>
+          <t>200750</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>170317</t>
+          <t>185235</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>200210</t>
+          <t>215679</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>268964</t>
+          <t>291186</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>249723</t>
+          <t>269789</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>286048</t>
+          <t>312929</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,56%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>197335</t>
+          <t>218079</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>185263</t>
+          <t>203334</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>208633</t>
+          <t>231470</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>239413</t>
+          <t>262317</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>224212</t>
+          <t>247388</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>254105</t>
+          <t>277832</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>436749</t>
+          <t>480396</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>419665</t>
+          <t>458653</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>455990</t>
+          <t>501793</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>65,03%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>281291</t>
+          <t>308515</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>281291</t>
+          <t>308515</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>281291</t>
+          <t>308515</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424422</t>
+          <t>463067</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424422</t>
+          <t>463067</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424422</t>
+          <t>463067</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>705713</t>
+          <t>771582</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>705713</t>
+          <t>771582</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>705713</t>
+          <t>771582</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>496170</t>
+          <t>571250</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>456947</t>
+          <t>526661</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>536612</t>
+          <t>616392</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>904961</t>
+          <t>798531</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>735655</t>
+          <t>761055</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1404661</t>
+          <t>840593</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1401131</t>
+          <t>1369781</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1219515</t>
+          <t>1311410</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1961677</t>
+          <t>1430828</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1673217</t>
+          <t>1804190</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1632775</t>
+          <t>1759048</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1712440</t>
+          <t>1848779</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2028751</t>
+          <t>2082821</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1529051</t>
+          <t>2040759</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2198057</t>
+          <t>2120297</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3701968</t>
+          <t>3887011</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3141422</t>
+          <t>3825964</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3883584</t>
+          <t>3945382</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>75,05%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2169387</t>
+          <t>2375440</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2169387</t>
+          <t>2375440</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2169387</t>
+          <t>2375440</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2933712</t>
+          <t>2881352</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2933712</t>
+          <t>2881352</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2933712</t>
+          <t>2881352</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>5103099</t>
+          <t>5256792</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5103099</t>
+          <t>5256792</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5103099</t>
+          <t>5256792</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">

--- a/data/trans_orig/P2B_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2B_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas que requieren dedicación o cuidados especiales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas que requieren dedicación o cuidados especiales en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas que requieren dedicación o cuidados especiales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2023 (tasa de respuesta: 99,84%)</t>
+          <t>Población según si convive con personas que requieren dedicación o cuidados especiales en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
